--- a/data/templates/项目功能点拆分表-模板.xlsx
+++ b/data/templates/项目功能点拆分表-模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="12111" windowHeight="19251" tabRatio="733" activeTab="2"/>
+    <workbookView windowWidth="32065" windowHeight="14725" tabRatio="733" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="模型说明" sheetId="10" r:id="rId1"/>
@@ -2052,7 +2052,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2084,6 +2084,17 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2288,7 +2299,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2298,6 +2309,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.349986266670736"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2760,136 +2777,136 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2897,11 +2914,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2971,55 +2988,61 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3040,46 +3063,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3542,48 +3565,48 @@
   </cols>
   <sheetData>
     <row r="1" ht="108.75" customHeight="1" spans="1:2">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="53"/>
+      <c r="B1" s="55"/>
     </row>
     <row r="4" ht="15" spans="1:2">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="57" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" ht="15" spans="1:2">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="57" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:2">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="55" t="s">
+      <c r="B6" s="57" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" ht="15" spans="1:2">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="57" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:2">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="55" t="s">
+      <c r="B8" s="57" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3607,398 +3630,398 @@
   </cols>
   <sheetData>
     <row r="1" ht="22.05" customHeight="1" spans="1:27">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="M1" s="40"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="M1" s="42"/>
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:27">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
     </row>
     <row r="3" ht="67" customHeight="1" spans="1:27">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="40"/>
-      <c r="W3" s="40"/>
-      <c r="X3" s="40"/>
-      <c r="Y3" s="40"/>
-      <c r="Z3" s="40"/>
-      <c r="AA3" s="40"/>
+      <c r="A3" s="43"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="42"/>
+      <c r="S3" s="42"/>
+      <c r="T3" s="42"/>
+      <c r="U3" s="42"/>
+      <c r="V3" s="42"/>
+      <c r="W3" s="42"/>
+      <c r="X3" s="42"/>
+      <c r="Y3" s="42"/>
+      <c r="Z3" s="42"/>
+      <c r="AA3" s="42"/>
     </row>
     <row r="4" ht="22.05" customHeight="1" spans="1:27">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="40"/>
-      <c r="S4" s="40"/>
-      <c r="T4" s="40"/>
-      <c r="U4" s="40"/>
-      <c r="V4" s="40"/>
-      <c r="W4" s="40"/>
-      <c r="X4" s="40"/>
-      <c r="Y4" s="40"/>
-      <c r="Z4" s="40"/>
-      <c r="AA4" s="40"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="42"/>
+      <c r="Q4" s="42"/>
+      <c r="R4" s="42"/>
+      <c r="S4" s="42"/>
+      <c r="T4" s="42"/>
+      <c r="U4" s="42"/>
+      <c r="V4" s="42"/>
+      <c r="W4" s="42"/>
+      <c r="X4" s="42"/>
+      <c r="Y4" s="42"/>
+      <c r="Z4" s="42"/>
+      <c r="AA4" s="42"/>
     </row>
     <row r="5" ht="29" customHeight="1" spans="1:27">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="40"/>
-      <c r="T5" s="40"/>
-      <c r="U5" s="40"/>
-      <c r="V5" s="40"/>
-      <c r="W5" s="40"/>
-      <c r="X5" s="40"/>
-      <c r="Y5" s="40"/>
-      <c r="Z5" s="40"/>
-      <c r="AA5" s="40"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
+      <c r="P5" s="42"/>
+      <c r="Q5" s="42"/>
+      <c r="R5" s="42"/>
+      <c r="S5" s="42"/>
+      <c r="T5" s="42"/>
+      <c r="U5" s="42"/>
+      <c r="V5" s="42"/>
+      <c r="W5" s="42"/>
+      <c r="X5" s="42"/>
+      <c r="Y5" s="42"/>
+      <c r="Z5" s="42"/>
+      <c r="AA5" s="42"/>
     </row>
     <row r="6" ht="82" customHeight="1" spans="1:27">
-      <c r="A6" s="41"/>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="40"/>
-      <c r="U6" s="40"/>
-      <c r="V6" s="40"/>
-      <c r="W6" s="40"/>
-      <c r="X6" s="40"/>
-      <c r="Y6" s="40"/>
-      <c r="Z6" s="40"/>
-      <c r="AA6" s="40"/>
+      <c r="A6" s="43"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="42"/>
+      <c r="R6" s="42"/>
+      <c r="S6" s="42"/>
+      <c r="T6" s="42"/>
+      <c r="U6" s="42"/>
+      <c r="V6" s="42"/>
+      <c r="W6" s="42"/>
+      <c r="X6" s="42"/>
+      <c r="Y6" s="42"/>
+      <c r="Z6" s="42"/>
+      <c r="AA6" s="42"/>
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:27">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="40"/>
-      <c r="S7" s="40"/>
-      <c r="T7" s="40"/>
-      <c r="U7" s="40"/>
-      <c r="V7" s="40"/>
-      <c r="W7" s="40"/>
-      <c r="X7" s="40"/>
-      <c r="Y7" s="40"/>
-      <c r="Z7" s="40"/>
-      <c r="AA7" s="40"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="42"/>
+      <c r="T7" s="42"/>
+      <c r="U7" s="42"/>
+      <c r="V7" s="42"/>
+      <c r="W7" s="42"/>
+      <c r="X7" s="42"/>
+      <c r="Y7" s="42"/>
+      <c r="Z7" s="42"/>
+      <c r="AA7" s="42"/>
     </row>
     <row r="8" ht="22.05" customHeight="1" spans="1:27">
-      <c r="A8" s="43"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43"/>
-      <c r="N8" s="40"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="40"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="40"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="40"/>
-      <c r="U8" s="40"/>
-      <c r="V8" s="40"/>
-      <c r="W8" s="40"/>
-      <c r="X8" s="40"/>
-      <c r="Y8" s="40"/>
-      <c r="Z8" s="40"/>
-      <c r="AA8" s="40"/>
+      <c r="A8" s="45"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45"/>
+      <c r="N8" s="42"/>
+      <c r="O8" s="42"/>
+      <c r="P8" s="42"/>
+      <c r="Q8" s="42"/>
+      <c r="R8" s="42"/>
+      <c r="S8" s="42"/>
+      <c r="T8" s="42"/>
+      <c r="U8" s="42"/>
+      <c r="V8" s="42"/>
+      <c r="W8" s="42"/>
+      <c r="X8" s="42"/>
+      <c r="Y8" s="42"/>
+      <c r="Z8" s="42"/>
+      <c r="AA8" s="42"/>
     </row>
     <row r="9" ht="302" customHeight="1" spans="1:27">
-      <c r="A9" s="43"/>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="43"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="43"/>
+      <c r="A9" s="45"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="45"/>
+      <c r="M9" s="45"/>
     </row>
     <row r="10" ht="22.05" customHeight="1" spans="1:27">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="44"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="44"/>
-      <c r="M10" s="44"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="46"/>
+      <c r="K10" s="46"/>
+      <c r="L10" s="46"/>
+      <c r="M10" s="46"/>
     </row>
     <row r="11" ht="22.05" customHeight="1" spans="1:27">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="45"/>
-      <c r="M11" s="45"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="47"/>
+      <c r="L11" s="47"/>
+      <c r="M11" s="47"/>
     </row>
     <row r="12" ht="22.05" customHeight="1" spans="1:27">
-      <c r="A12" s="45"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="45"/>
+      <c r="A12" s="47"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="47"/>
     </row>
     <row r="13" ht="22.05" customHeight="1" spans="1:27">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="45"/>
-      <c r="M13" s="45"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="47"/>
     </row>
     <row r="14" ht="409" customHeight="1" spans="1:27">
-      <c r="A14" s="45"/>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="45"/>
-      <c r="L14" s="45"/>
-      <c r="M14" s="45"/>
+      <c r="A14" s="47"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47"/>
     </row>
     <row r="15" ht="22.05" customHeight="1" spans="1:27">
-      <c r="A15" s="44" t="s">
+      <c r="A15" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="44"/>
-      <c r="L15" s="44"/>
-      <c r="M15" s="44"/>
+      <c r="B15" s="46"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
+      <c r="L15" s="46"/>
+      <c r="M15" s="46"/>
     </row>
     <row r="16" ht="22.05" customHeight="1" spans="1:27">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="45"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="45"/>
-      <c r="M16" s="45"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="47"/>
+      <c r="L16" s="47"/>
+      <c r="M16" s="47"/>
     </row>
     <row r="17" ht="22.05" customHeight="1" spans="1:14">
-      <c r="A17" s="45"/>
-      <c r="B17" s="45"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="45"/>
-      <c r="L17" s="45"/>
-      <c r="M17" s="45"/>
+      <c r="A17" s="47"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="47"/>
+      <c r="L17" s="47"/>
+      <c r="M17" s="47"/>
     </row>
     <row r="18" ht="22.05" customHeight="1" spans="1:14">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45"/>
-      <c r="M18" s="45"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="47"/>
+      <c r="M18" s="47"/>
     </row>
     <row r="19" ht="22.05" customHeight="1" spans="1:14">
       <c r="A19" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="46"/>
-      <c r="C19" s="47" t="s">
+      <c r="B19" s="48"/>
+      <c r="C19" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="48"/>
+      <c r="D19" s="50"/>
     </row>
     <row r="20" ht="22.05" customHeight="1" spans="1:14">
-      <c r="A20" s="47"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="47" t="s">
+      <c r="A20" s="49"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="47"/>
+      <c r="D20" s="49"/>
     </row>
     <row r="21" ht="22.05" customHeight="1" spans="1:14">
-      <c r="A21" s="47"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="47" t="s">
+      <c r="A21" s="49"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="47"/>
-      <c r="N21" s="51"/>
+      <c r="D21" s="49"/>
+      <c r="N21" s="53"/>
     </row>
     <row r="22" ht="22.05" customHeight="1" spans="1:14">
-      <c r="A22" s="47"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="N22" s="51"/>
+      <c r="A22" s="49"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="N22" s="53"/>
     </row>
     <row r="23" ht="22.05" customHeight="1"/>
     <row r="24" ht="22.05" customHeight="1"/>
     <row r="25" ht="22.05" customHeight="1" spans="1:14">
-      <c r="A25" s="39" t="s">
+      <c r="A25" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
     </row>
     <row r="26" ht="22.05" customHeight="1" spans="1:14">
       <c r="A26" t="s">
@@ -11223,36 +11246,36 @@
       </c>
     </row>
     <row r="247" s="2" customFormat="1" ht="14.1" spans="1:13">
-      <c r="A247" s="31" t="s">
+      <c r="A247" s="39" t="s">
         <v>656</v>
       </c>
-      <c r="B247" s="31"/>
-      <c r="C247" s="36"/>
-      <c r="D247" s="36"/>
-      <c r="E247" s="36"/>
-      <c r="F247" s="36"/>
-      <c r="G247" s="36"/>
-      <c r="H247" s="31"/>
-      <c r="I247" s="36"/>
-      <c r="J247" s="31"/>
-      <c r="K247" s="31"/>
-      <c r="L247" s="31"/>
-      <c r="M247" s="31"/>
+      <c r="B247" s="39"/>
+      <c r="C247" s="40"/>
+      <c r="D247" s="40"/>
+      <c r="E247" s="40"/>
+      <c r="F247" s="40"/>
+      <c r="G247" s="40"/>
+      <c r="H247" s="39"/>
+      <c r="I247" s="40"/>
+      <c r="J247" s="39"/>
+      <c r="K247" s="39"/>
+      <c r="L247" s="39"/>
+      <c r="M247" s="39"/>
     </row>
     <row r="248" s="2" customFormat="1" ht="156" customHeight="1" spans="1:13">
-      <c r="A248" s="31"/>
-      <c r="B248" s="31"/>
-      <c r="C248" s="36"/>
-      <c r="D248" s="36"/>
-      <c r="E248" s="36"/>
-      <c r="F248" s="36"/>
-      <c r="G248" s="36"/>
-      <c r="H248" s="31"/>
-      <c r="I248" s="36"/>
-      <c r="J248" s="31"/>
-      <c r="K248" s="31"/>
-      <c r="L248" s="31"/>
-      <c r="M248" s="31"/>
+      <c r="A248" s="39"/>
+      <c r="B248" s="39"/>
+      <c r="C248" s="40"/>
+      <c r="D248" s="40"/>
+      <c r="E248" s="40"/>
+      <c r="F248" s="40"/>
+      <c r="G248" s="40"/>
+      <c r="H248" s="39"/>
+      <c r="I248" s="40"/>
+      <c r="J248" s="39"/>
+      <c r="K248" s="39"/>
+      <c r="L248" s="39"/>
+      <c r="M248" s="39"/>
     </row>
     <row r="249" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="A249" s="5"/>

--- a/data/templates/项目功能点拆分表-模板.xlsx
+++ b/data/templates/项目功能点拆分表-模板.xlsx
@@ -5417,7 +5417,7 @@
         <v>67</v>
       </c>
       <c r="M77" s="28">
-        <f t="shared" ref="M77:M79" si="5">IF(L77="新增",1,IF(L77="复用",1/3,IF(L77="利旧",0)))</f>
+        <f t="shared" ref="M77:M81" si="5">IF(L77="新增",1,IF(L77="复用",1/3,IF(L77="利旧",0)))</f>
         <v>1</v>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
         <v>67</v>
       </c>
       <c r="M78" s="28">
-        <f>IF(L78="新增",1,IF(L78="复用",1/3,IF(L78="利旧",0)))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -5473,7 +5473,7 @@
         <v>67</v>
       </c>
       <c r="M79" s="28">
-        <f>IF(L79="新增",1,IF(L79="复用",1/3,IF(L79="利旧",0)))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
         <v>67</v>
       </c>
       <c r="M80" s="28">
-        <f>IF(L80="新增",1,IF(L80="复用",1/3,IF(L80="利旧",0)))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
         <v>67</v>
       </c>
       <c r="M81" s="28">
-        <f>IF(L81="新增",1,IF(L81="复用",1/3,IF(L81="利旧",0)))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -22026,7 +22026,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="474"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:L44 L45:L79 L80:L104">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:L104">
       <formula1>"新增,复用,利旧"</formula1>
     </dataValidation>
   </dataValidations>
